--- a/data/trans_camb/P43C-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P43C-Provincia-trans_camb.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,9 +515,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -529,25 +526,18 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -578,21 +568,6 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023/2007</t>
         </is>
@@ -607,9 +582,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -624,17 +596,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14,32</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13,94</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33,29</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -648,21 +620,6 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>33,29</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,32</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13,94</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>33,29</t>
         </is>
@@ -677,47 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,3; 23,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,25; 22,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,57; 41,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,11; 23,59</t>
+          <t>5,3; 23,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,72; 22,0</t>
+          <t>5,25; 22,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,46; 40,37</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,11; 23,59</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5,72; 22,0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>23,46; 40,37</t>
+          <t>23,57; 41,05</t>
         </is>
       </c>
     </row>
@@ -730,17 +672,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -754,21 +696,6 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>57,96%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>24,93%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>24,27%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>57,96%</t>
         </is>
@@ -783,47 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,92; 46,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,28; 42,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>38,49; 80,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,97; 44,67</t>
+          <t>8,92; 46,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,28; 41,9</t>
+          <t>8,28; 42,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,8; 77,79</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,97; 44,67</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9,28; 41,9</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>37,8; 77,79</t>
+          <t>38,49; 80,3</t>
         </is>
       </c>
     </row>
@@ -840,17 +752,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18,51</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19,18</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,97</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -864,21 +776,6 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,97</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18,51</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>19,18</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>3,97</t>
         </is>
@@ -893,47 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,05; 24,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,51; 25,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,49; 9,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,32; 24,1</t>
+          <t>12,05; 24,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,88; 24,82</t>
+          <t>12,51; 25,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 10,59</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>12,32; 24,1</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>12,88; 24,82</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>-2,47; 10,59</t>
+          <t>-2,49; 9,84</t>
         </is>
       </c>
     </row>
@@ -946,17 +828,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -970,21 +852,6 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>33,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>35,12%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7,26%</t>
         </is>
@@ -999,47 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,37; 48,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,75; 48,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,4; 18,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,91; 46,87</t>
+          <t>20,37; 48,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,9; 48,06</t>
+          <t>21,75; 48,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 21,0</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>20,91; 46,87</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>21,9; 48,06</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>-4,3; 21,0</t>
+          <t>-4,4; 18,99</t>
         </is>
       </c>
     </row>
@@ -1056,17 +908,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22,04</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,77</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1080,21 +932,6 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,77</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>22,04</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>5,77</t>
         </is>
@@ -1109,47 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,32; 7,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,83; 29,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,99; 13,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 7,81</t>
+          <t>-8,32; 7,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,21; 28,64</t>
+          <t>14,83; 29,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 13,61</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-7,55; 7,81</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15,21; 28,64</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>-1,46; 13,61</t>
+          <t>-1,99; 13,09</t>
         </is>
       </c>
     </row>
@@ -1162,17 +984,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-0,19%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1186,21 +1008,6 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-0,19%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>38,84%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>10,18%</t>
         </is>
@@ -1215,47 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,77; 14,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>25,04; 56,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,75; 25,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 14,8</t>
+          <t>-13,77; 14,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,09; 55,67</t>
+          <t>25,04; 56,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 26,33</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-12,7; 14,8</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>25,09; 55,67</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>-2,36; 26,33</t>
+          <t>-2,75; 25,61</t>
         </is>
       </c>
     </row>
@@ -1272,17 +1064,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,56</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13,36</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19,37</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1296,21 +1088,6 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>19,37</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,56</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>13,36</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>19,37</t>
         </is>
@@ -1325,47 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,24; 17,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,73; 20,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,79; 32,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,96; 17,54</t>
+          <t>3,24; 17,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,28; 19,61</t>
+          <t>6,73; 20,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,93; 31,67</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2,96; 17,54</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>6,28; 19,61</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>8,93; 31,67</t>
+          <t>8,79; 32,47</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1140,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1402,21 +1164,6 @@
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>34,25%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>18,67%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>23,63%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>34,25%</t>
         </is>
@@ -1431,47 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,57; 32,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,24; 38,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,68; 60,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,65; 33,1</t>
+          <t>5,57; 32,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,03; 36,87</t>
+          <t>11,24; 38,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,31; 59,89</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,65; 33,1</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>10,03; 36,87</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>15,31; 59,89</t>
+          <t>14,68; 60,88</t>
         </is>
       </c>
     </row>
@@ -1488,17 +1220,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21,35</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,11</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2,02</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1512,21 +1244,6 @@
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-2,02</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>21,35</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2,11</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>-2,02</t>
         </is>
@@ -1541,47 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,43; 30,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,4; 12,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,52; 6,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,98; 30,97</t>
+          <t>11,43; 30,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 10,45</t>
+          <t>-7,4; 12,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 5,97</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>11,98; 30,97</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-8,61; 10,45</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>-11,45; 5,97</t>
+          <t>-10,52; 6,31</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1296,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-4,84%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1618,21 +1320,6 @@
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-4,84%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>51,09%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>-4,84%</t>
         </is>
@@ -1647,47 +1334,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,59; 84,72</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-16,01; 36,35</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-21,82; 17,57</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25,19; 84,74</t>
+          <t>23,59; 84,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 27,91</t>
+          <t>-16,01; 36,35</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 16,54</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>25,19; 84,74</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-17,96; 27,91</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>-23,77; 16,54</t>
+          <t>-21,82; 17,57</t>
         </is>
       </c>
     </row>
@@ -1704,17 +1376,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,15</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-23,15</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5,16</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1728,21 +1400,6 @@
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-5,16</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>8,15</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-23,15</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>-5,16</t>
         </is>
@@ -1757,47 +1414,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,51; 16,9</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-30,22; -15,13</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-12,7; 2,83</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 16,46</t>
+          <t>-0,51; 16,9</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-30,94; -14,4</t>
+          <t>-30,22; -15,13</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 2,86</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-0,65; 16,46</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-30,94; -14,4</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>-13,09; 2,86</t>
+          <t>-12,7; 2,83</t>
         </is>
       </c>
     </row>
@@ -1810,17 +1452,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-49,95%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-11,14%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1834,21 +1476,6 @@
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-11,14%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>17,58%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-49,95%</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>-11,14%</t>
         </is>
@@ -1863,47 +1490,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,45; 41,26</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-60,71; -35,54</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-25,71; 6,41</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 40,05</t>
+          <t>-0,45; 41,26</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-61,0; -35,19</t>
+          <t>-60,71; -35,54</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-25,93; 6,63</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-1,37; 40,05</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-61,0; -35,19</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>-25,93; 6,63</t>
+          <t>-25,71; 6,41</t>
         </is>
       </c>
     </row>
@@ -1920,17 +1532,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,21</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1,55</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-12,21</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1944,21 +1556,6 @@
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-12,21</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,21</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-1,55</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>-12,21</t>
         </is>
@@ -1973,47 +1570,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,52; 6,01</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,7; 3,74</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-41,43; 12,45</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 5,34</t>
+          <t>-4,52; 6,01</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 4,33</t>
+          <t>-6,7; 3,74</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-43,83; 12,81</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-4,82; 5,34</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-6,52; 4,33</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>-43,83; 12,81</t>
+          <t>-41,43; 12,45</t>
         </is>
       </c>
     </row>
@@ -2026,17 +1608,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-2,45%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-19,22%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2050,21 +1632,6 @@
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-19,22%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-2,45%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>-19,22%</t>
         </is>
@@ -2079,47 +1646,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,69; 9,63</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,07; 6,14</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-64,97; 19,75</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 8,86</t>
+          <t>-6,69; 9,63</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 7,1</t>
+          <t>-10,07; 6,14</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-68,84; 20,5</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-7,26; 8,86</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-9,83; 7,1</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>-68,84; 20,5</t>
+          <t>-64,97; 19,75</t>
         </is>
       </c>
     </row>
@@ -2136,17 +1688,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18,34</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19,38</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5,48</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2160,21 +1712,6 @@
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-5,48</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>18,34</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>19,38</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>-5,48</t>
         </is>
@@ -2189,47 +1726,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,7; 23,3</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,28; 24,18</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,63; -0,59</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>13,08; 23,16</t>
+          <t>12,7; 23,3</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>14,55; 24,71</t>
+          <t>14,28; 24,18</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-10,42; -0,03</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>13,08; 23,16</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>14,55; 24,71</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>-10,42; -0,03</t>
+          <t>-10,63; -0,59</t>
         </is>
       </c>
     </row>
@@ -2242,17 +1764,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-11,59%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2266,21 +1788,6 @@
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-11,59%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>38,79%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>41,01%</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>-11,59%</t>
         </is>
@@ -2295,47 +1802,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>25,72; 52,8</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>28,57; 54,46</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-21,38; -1,66</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>25,73; 51,56</t>
+          <t>25,72; 52,8</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>28,79; 56,12</t>
+          <t>28,57; 54,46</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-20,96; -0,07</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>25,73; 51,56</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>28,79; 56,12</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>-20,96; -0,07</t>
+          <t>-21,38; -1,66</t>
         </is>
       </c>
     </row>
@@ -2352,17 +1844,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11,29</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,13</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,16</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2376,21 +1868,6 @@
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>2,16</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>11,29</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>10,13</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>2,16</t>
         </is>
@@ -2405,47 +1882,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,89; 13,51</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,82; 12,42</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-12,99; 7,8</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>8,86; 13,63</t>
+          <t>8,89; 13,51</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>7,95; 12,56</t>
+          <t>7,82; 12,42</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 7,85</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>8,86; 13,63</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>7,95; 12,56</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>-10,19; 7,85</t>
+          <t>-12,99; 7,8</t>
         </is>
       </c>
     </row>
@@ -2458,17 +1920,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2482,21 +1944,6 @@
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>4,01%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>20,97%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>18,82%</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>4,01%</t>
         </is>
@@ -2511,47 +1958,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,14; 25,63</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,23; 23,63</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-23,65; 14,55</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>16,13; 26,12</t>
+          <t>16,14; 25,63</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>14,45; 23,75</t>
+          <t>14,23; 23,63</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 14,66</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>16,13; 26,12</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>14,45; 23,75</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>-18,72; 14,66</t>
+          <t>-23,65; 14,55</t>
         </is>
       </c>
     </row>
@@ -2563,7 +1995,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
@@ -2571,7 +2003,6 @@
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>

--- a/data/trans_camb/P43C-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P43C-Provincia-trans_camb.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33,29</t>
+          <t>32,11</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,29</t>
+          <t>32,11</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,3; 23,59</t>
+          <t>5,32; 22,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,25; 22,43</t>
+          <t>5,68; 21,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,57; 41,05</t>
+          <t>23,95; 39,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,3; 23,59</t>
+          <t>5,32; 22,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,25; 22,43</t>
+          <t>5,68; 21,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,57; 41,05</t>
+          <t>23,95; 39,01</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>55,89%</t>
         </is>
       </c>
     </row>
@@ -710,32 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,92; 46,51</t>
+          <t>8,57; 42,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,28; 42,95</t>
+          <t>8,88; 41,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38,49; 80,3</t>
+          <t>38,28; 76,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,92; 46,51</t>
+          <t>8,57; 42,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,28; 42,95</t>
+          <t>8,88; 41,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,49; 80,3</t>
+          <t>38,28; 76,88</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,97</t>
+          <t>2,86</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,97</t>
+          <t>2,86</t>
         </is>
       </c>
     </row>
@@ -790,32 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,05; 24,66</t>
+          <t>12,21; 24,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,51; 25,06</t>
+          <t>12,71; 25,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 9,84</t>
+          <t>-3,16; 9,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,05; 24,66</t>
+          <t>12,21; 24,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,51; 25,06</t>
+          <t>12,71; 25,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 9,84</t>
+          <t>-3,16; 9,04</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -866,32 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,37; 48,68</t>
+          <t>20,68; 46,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,75; 48,93</t>
+          <t>22,64; 49,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 18,99</t>
+          <t>-5,52; 17,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,37; 48,68</t>
+          <t>20,68; 46,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,75; 48,93</t>
+          <t>22,64; 49,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 18,99</t>
+          <t>-5,52; 17,88</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,77</t>
+          <t>6,21</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,77</t>
+          <t>6,21</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 7,59</t>
+          <t>-7,07; 7,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,83; 29,08</t>
+          <t>15,18; 29,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 13,09</t>
+          <t>-1,23; 13,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 7,59</t>
+          <t>-7,07; 7,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,83; 29,08</t>
+          <t>15,18; 29,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 13,09</t>
+          <t>-1,23; 13,45</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -1022,32 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 14,5</t>
+          <t>-11,78; 15,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25,04; 56,29</t>
+          <t>25,35; 56,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 25,61</t>
+          <t>-2,08; 25,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 14,5</t>
+          <t>-11,78; 15,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,04; 56,29</t>
+          <t>25,35; 56,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 25,61</t>
+          <t>-2,08; 25,58</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19,37</t>
+          <t>9,53</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,37</t>
+          <t>9,53</t>
         </is>
       </c>
     </row>
@@ -1102,32 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,24; 17,21</t>
+          <t>3,65; 17,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,73; 20,15</t>
+          <t>6,46; 20,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,79; 32,47</t>
+          <t>1,53; 17,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,24; 17,21</t>
+          <t>3,65; 17,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,73; 20,15</t>
+          <t>6,46; 20,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,79; 32,47</t>
+          <t>1,53; 17,02</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -1178,32 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,57; 32,96</t>
+          <t>6,29; 34,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,24; 38,95</t>
+          <t>10,65; 38,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,68; 60,88</t>
+          <t>2,59; 32,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,57; 32,96</t>
+          <t>6,29; 34,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,24; 38,95</t>
+          <t>10,65; 38,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,68; 60,88</t>
+          <t>2,59; 32,22</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,02</t>
+          <t>-2,31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,02</t>
+          <t>-2,31</t>
         </is>
       </c>
     </row>
@@ -1258,32 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11,43; 30,82</t>
+          <t>11,7; 30,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 12,85</t>
+          <t>-7,92; 11,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 6,31</t>
+          <t>-10,74; 6,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,43; 30,82</t>
+          <t>11,7; 30,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 12,85</t>
+          <t>-7,92; 11,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 6,31</t>
+          <t>-10,74; 6,1</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-4,84%</t>
+          <t>-5,54%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-4,84%</t>
+          <t>-5,54%</t>
         </is>
       </c>
     </row>
@@ -1334,32 +1334,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>23,59; 84,72</t>
+          <t>24,96; 84,75</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 36,35</t>
+          <t>-16,59; 32,08</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,82; 17,57</t>
+          <t>-22,71; 17,04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23,59; 84,72</t>
+          <t>24,96; 84,75</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 36,35</t>
+          <t>-16,59; 32,08</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-21,82; 17,57</t>
+          <t>-22,71; 17,04</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-5,16</t>
+          <t>-4,92</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-5,16</t>
+          <t>-4,92</t>
         </is>
       </c>
     </row>
@@ -1414,32 +1414,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 16,9</t>
+          <t>-0,91; 15,93</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-30,22; -15,13</t>
+          <t>-31,1; -15,17</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 2,83</t>
+          <t>-13,29; 3,42</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 16,9</t>
+          <t>-0,91; 15,93</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-30,22; -15,13</t>
+          <t>-31,1; -15,17</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 2,83</t>
+          <t>-13,29; 3,42</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-11,14%</t>
+          <t>-10,62%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-11,14%</t>
+          <t>-10,62%</t>
         </is>
       </c>
     </row>
@@ -1490,32 +1490,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 41,26</t>
+          <t>-1,56; 38,04</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-60,71; -35,54</t>
+          <t>-62,47; -36,4</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-25,71; 6,41</t>
+          <t>-25,97; 8,35</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 41,26</t>
+          <t>-1,56; 38,04</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-60,71; -35,54</t>
+          <t>-62,47; -36,4</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-25,71; 6,41</t>
+          <t>-25,97; 8,35</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-12,21</t>
+          <t>10,23</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-12,21</t>
+          <t>10,23</t>
         </is>
       </c>
     </row>
@@ -1570,32 +1570,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 6,01</t>
+          <t>-5,31; 5,65</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 3,74</t>
+          <t>-6,9; 4,09</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-41,43; 12,45</t>
+          <t>4,42; 15,38</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 6,01</t>
+          <t>-5,31; 5,65</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 3,74</t>
+          <t>-6,9; 4,09</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-41,43; 12,45</t>
+          <t>4,42; 15,38</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-19,22%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-19,22%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -1646,32 +1646,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 9,63</t>
+          <t>-8,13; 9,38</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 6,14</t>
+          <t>-10,48; 6,52</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-64,97; 19,75</t>
+          <t>6,57; 25,27</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 9,63</t>
+          <t>-8,13; 9,38</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 6,14</t>
+          <t>-10,48; 6,52</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-64,97; 19,75</t>
+          <t>6,57; 25,27</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-5,48</t>
+          <t>-7,26</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-5,48</t>
+          <t>-7,26</t>
         </is>
       </c>
     </row>
@@ -1726,32 +1726,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>12,7; 23,3</t>
+          <t>13,23; 23,51</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>14,28; 24,18</t>
+          <t>14,09; 24,16</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-10,63; -0,59</t>
+          <t>-12,3; -2,33</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>12,7; 23,3</t>
+          <t>13,23; 23,51</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>14,28; 24,18</t>
+          <t>14,09; 24,16</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-10,63; -0,59</t>
+          <t>-12,3; -2,33</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-11,59%</t>
+          <t>-15,35%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-11,59%</t>
+          <t>-15,35%</t>
         </is>
       </c>
     </row>
@@ -1802,32 +1802,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>25,72; 52,8</t>
+          <t>26,43; 53,36</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>28,57; 54,46</t>
+          <t>28,04; 54,33</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-21,38; -1,66</t>
+          <t>-24,73; -5,31</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>25,72; 52,8</t>
+          <t>26,43; 53,36</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>28,57; 54,46</t>
+          <t>28,04; 54,33</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-21,38; -1,66</t>
+          <t>-24,73; -5,31</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>4,13</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>4,13</t>
         </is>
       </c>
     </row>
@@ -1882,32 +1882,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>8,89; 13,51</t>
+          <t>8,68; 13,54</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>7,82; 12,42</t>
+          <t>7,75; 12,68</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 7,8</t>
+          <t>1,49; 6,45</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>8,89; 13,51</t>
+          <t>8,68; 13,54</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>7,82; 12,42</t>
+          <t>7,75; 12,68</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 7,8</t>
+          <t>1,49; 6,45</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -1958,32 +1958,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>16,14; 25,63</t>
+          <t>15,8; 25,81</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>14,23; 23,63</t>
+          <t>14,21; 24,24</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-23,65; 14,55</t>
+          <t>2,77; 12,26</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>16,14; 25,63</t>
+          <t>15,8; 25,81</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>14,23; 23,63</t>
+          <t>14,21; 24,24</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-23,65; 14,55</t>
+          <t>2,77; 12,26</t>
         </is>
       </c>
     </row>
